--- a/AIGGPA_Fieldwork_Review/Department_Wise_Analysis/Rural_Development/Rural_Development_Descriptive_Statistics.xlsx
+++ b/AIGGPA_Fieldwork_Review/Department_Wise_Analysis/Rural_Development/Rural_Development_Descriptive_Statistics.xlsx
@@ -566,16 +566,16 @@
         <v>4</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>2.67</v>
+        <v>4</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="3">
@@ -603,16 +603,16 @@
         <v>4</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>2.85</v>
+        <v>3.67</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="4">
@@ -640,16 +640,16 @@
         <v>5</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>2.77</v>
+        <v>4.33</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="5">
@@ -677,16 +677,16 @@
         <v>4</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>2.52</v>
+        <v>4</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="6">
@@ -714,16 +714,16 @@
         <v>5</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>3.38</v>
+        <v>1</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="7">
@@ -751,16 +751,16 @@
         <v>5</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>2.6</v>
+        <v>4.67</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="8">
@@ -788,16 +788,16 @@
         <v>5</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>2.42</v>
+        <v>4.33</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="9">
@@ -825,16 +825,16 @@
         <v>5</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>2.35</v>
+        <v>4.33</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="10">
@@ -862,16 +862,16 @@
         <v>5</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>2.73</v>
+        <v>4</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="11">
@@ -899,16 +899,16 @@
         <v>5</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>2.12</v>
+        <v>3.33</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="12">
@@ -936,16 +936,16 @@
         <v>5</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>2.65</v>
+        <v>4.67</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="13">
@@ -973,16 +973,16 @@
         <v>5</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>2.4</v>
+        <v>4.33</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="14">
@@ -1010,16 +1010,16 @@
         <v>4</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>1.6</v>
+        <v>2.67</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1047,16 +1047,16 @@
         <v>5</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1084,16 +1084,16 @@
         <v>4</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>2.27</v>
+        <v>4</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="17">
@@ -1121,16 +1121,16 @@
         <v>5</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>2.65</v>
+        <v>4.33</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="18">
@@ -1158,16 +1158,16 @@
         <v>5</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>2.33</v>
+        <v>4.33</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1195,16 +1195,16 @@
         <v>5</v>
       </c>
       <c r="H19" s="3" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J19" s="3" t="n">
         <v>2.65</v>
       </c>
-      <c r="I19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="K19" s="3" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="20">
@@ -1232,16 +1232,16 @@
         <v>5</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>3.83</v>
+        <v>2.33</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="21">
@@ -1269,16 +1269,16 @@
         <v>5</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>2.83</v>
+        <v>1.33</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="22">
@@ -1306,16 +1306,16 @@
         <v>5</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>2.3</v>
+        <v>3.67</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
     </row>
   </sheetData>
